--- a/data/orders_synthetic.xlsx
+++ b/data/orders_synthetic.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>客戶A</t>
+          <t>福氣輪業股份有限公司</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -530,7 +530,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>客戶B</t>
+          <t>金旺來工業社</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -561,7 +561,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>客戶C</t>
+          <t>大力出奇蹟實業有限公司</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -592,7 +592,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>客戶D</t>
+          <t>永固機械股份有限公司</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -623,7 +623,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>客戶D</t>
+          <t>永固機械股份有限公司</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>客戶E</t>
+          <t>黑狗兄輪業商社</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -685,7 +685,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>客戶E</t>
+          <t>黑狗兄輪業商社</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>客戶F</t>
+          <t>好運輪輪來企業社</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>客戶G</t>
+          <t>鐵牛運搬股份有限公司</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>客戶D</t>
+          <t>永固機械股份有限公司</t>
         </is>
       </c>
       <c r="H11" t="n">
